--- a/jaspr/web/cicada_ig/StructureDefinition-Vaccine.xlsx
+++ b/jaspr/web/cicada_ig/StructureDefinition-Vaccine.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T14:37:07-05:00</t>
+    <t>2026-09-02T22:18:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jaspr/web/cicada_ig/StructureDefinition-Vaccine.xlsx
+++ b/jaspr/web/cicada_ig/StructureDefinition-Vaccine.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/fhir/StructureDefinition/Vaccine</t>
+    <t>http://fhirfli.dev/fhir/ig/cicada/StructureDefinition/Vaccine</t>
   </si>
   <si>
     <t>Version</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T22:18:14-04:00</t>
+    <t>2026-09-06T20:44:07-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jaspr/web/cicada_ig/StructureDefinition-Vaccine.xlsx
+++ b/jaspr/web/cicada_ig/StructureDefinition-Vaccine.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-06T20:44:07-04:00</t>
+    <t>2026-09-06T23:13:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jaspr/web/cicada_ig/StructureDefinition-Vaccine.xlsx
+++ b/jaspr/web/cicada_ig/StructureDefinition-Vaccine.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-06T23:13:14-04:00</t>
+    <t>2026-09-07T18:40:23-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jaspr/web/cicada_ig/StructureDefinition-Vaccine.xlsx
+++ b/jaspr/web/cicada_ig/StructureDefinition-Vaccine.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="331">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T18:40:23-04:00</t>
+    <t>2026-09-07T19:28:06-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Simple vaccine to easily obtain needed information for forecasting</t>
+    <t>A vaccine product as CDC's supporting data describes one: the CVX, the trade name, the ages between which it is a preferable vaccine, and its type. Note that beginAge and endAge are FHIR Age values, which must be positive (age-1), so CDC's "0 days" cannot be carried; a begin age of 0 days is expressed by omitting beginAge.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -537,7 +537,7 @@
     <t>The serial number could be included as an identifier.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:type}
+    <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
@@ -551,6 +551,9 @@
   </si>
   <si>
     <t>tradeName</t>
+  </si>
+  <si>
+    <t>The vaccine's trade name</t>
   </si>
   <si>
     <t>Medication.identifier:tradeName.id</t>
@@ -648,13 +651,6 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;code value="official"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
     <t>extensible</t>
   </si>
   <si>
@@ -686,6 +682,9 @@
   </si>
   <si>
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://fhirfli.dev/fhir/ig/cicada/identifier/trade-name</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -3027,7 +3026,7 @@
         <v>161</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
         <v>163</v>
@@ -3112,10 +3111,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3138,13 +3137,13 @@
         <v>19</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3195,7 +3194,7 @@
         <v>19</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3213,7 +3212,7 @@
         <v>19</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>19</v>
@@ -3224,10 +3223,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3253,10 +3252,10 @@
         <v>130</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>157</v>
@@ -3300,7 +3299,7 @@
         <v>133</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>19</v>
@@ -3309,7 +3308,7 @@
         <v>134</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3327,7 +3326,7 @@
         <v>19</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>19</v>
@@ -3338,10 +3337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3367,16 +3366,16 @@
         <v>105</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>19</v>
@@ -3401,13 +3400,13 @@
         <v>19</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>19</v>
@@ -3425,7 +3424,7 @@
         <v>19</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3443,7 +3442,7 @@
         <v>19</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>19</v>
@@ -3454,10 +3453,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3465,7 +3464,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>85</v>
@@ -3480,19 +3479,19 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>19</v>
@@ -3502,7 +3501,7 @@
         <v>19</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>201</v>
+        <v>19</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>19</v>
@@ -3559,7 +3558,7 @@
         <v>19</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>19</v>
@@ -3581,7 +3580,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>85</v>
@@ -3618,10 +3617,10 @@
         <v>19</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>19</v>
+        <v>213</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U20" t="s" s="2">
         <v>19</v>
@@ -3657,7 +3656,7 @@
         <v>19</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3675,21 +3674,21 @@
         <v>19</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3712,16 +3711,16 @@
         <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3735,7 +3734,7 @@
         <v>19</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>19</v>
@@ -3771,7 +3770,7 @@
         <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3789,21 +3788,21 @@
         <v>19</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3826,13 +3825,13 @@
         <v>86</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3883,7 +3882,7 @@
         <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3901,21 +3900,21 @@
         <v>19</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3938,16 +3937,16 @@
         <v>86</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3997,7 +3996,7 @@
         <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4015,21 +4014,21 @@
         <v>19</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4052,16 +4051,16 @@
         <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4087,13 +4086,13 @@
         <v>19</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>19</v>
@@ -4111,7 +4110,7 @@
         <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4126,24 +4125,24 @@
         <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4169,13 +4168,13 @@
         <v>105</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4201,13 +4200,13 @@
         <v>19</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>19</v>
@@ -4225,7 +4224,7 @@
         <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4243,7 +4242,7 @@
         <v>19</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>19</v>
@@ -4254,10 +4253,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4280,13 +4279,13 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4337,7 +4336,7 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4352,24 +4351,24 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4392,16 +4391,16 @@
         <v>19</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4427,13 +4426,13 @@
         <v>19</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>19</v>
@@ -4451,7 +4450,7 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4466,24 +4465,24 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4506,13 +4505,13 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4563,7 +4562,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4581,7 +4580,7 @@
         <v>19</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>19</v>
@@ -4592,10 +4591,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4618,16 +4617,16 @@
         <v>19</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4677,7 +4676,7 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4695,7 +4694,7 @@
         <v>19</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>19</v>
@@ -4706,10 +4705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4732,13 +4731,13 @@
         <v>19</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4789,7 +4788,7 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4807,7 +4806,7 @@
         <v>19</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>19</v>
@@ -4818,10 +4817,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4847,10 +4846,10 @@
         <v>130</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>157</v>
@@ -4903,7 +4902,7 @@
         <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4921,7 +4920,7 @@
         <v>19</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>19</v>
@@ -4932,14 +4931,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4961,10 +4960,10 @@
         <v>130</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>157</v>
@@ -5019,7 +5018,7 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5048,10 +5047,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5074,17 +5073,17 @@
         <v>19</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>19</v>
@@ -5133,7 +5132,7 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>85</v>
@@ -5148,24 +5147,24 @@
         <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5188,17 +5187,17 @@
         <v>19</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>19</v>
@@ -5247,7 +5246,7 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5265,7 +5264,7 @@
         <v>19</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>19</v>
@@ -5276,10 +5275,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5302,13 +5301,13 @@
         <v>19</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5359,7 +5358,7 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5374,24 +5373,24 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5414,13 +5413,13 @@
         <v>19</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5471,7 +5470,7 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5486,10 +5485,10 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>19</v>
@@ -5500,10 +5499,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5526,13 +5525,13 @@
         <v>19</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5583,7 +5582,7 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5601,7 +5600,7 @@
         <v>19</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>19</v>
@@ -5612,10 +5611,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5641,10 +5640,10 @@
         <v>130</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>157</v>
@@ -5697,7 +5696,7 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5715,7 +5714,7 @@
         <v>19</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>19</v>
@@ -5726,14 +5725,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5755,10 +5754,10 @@
         <v>130</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>157</v>
@@ -5813,7 +5812,7 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5842,10 +5841,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5868,13 +5867,13 @@
         <v>19</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5925,7 +5924,7 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5940,7 +5939,7 @@
         <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>166</v>
@@ -5949,15 +5948,15 @@
         <v>19</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5980,13 +5979,13 @@
         <v>19</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6037,7 +6036,7 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6052,16 +6051,16 @@
         <v>97</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>

--- a/jaspr/web/cicada_ig/StructureDefinition-Vaccine.xlsx
+++ b/jaspr/web/cicada_ig/StructureDefinition-Vaccine.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T19:28:06-04:00</t>
+    <t>2026-09-07T19:51:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
